--- a/metadata/plate_metadata/20260416_cep290_30to48hpf_plate02_t02_well_metadata.xlsx
+++ b/metadata/plate_metadata/20260416_cep290_30to48hpf_plate02_t02_well_metadata.xlsx
@@ -1901,7 +1901,7 @@
       </c>
       <c r="C2" s="10" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="D2" s="9" t="inlineStr">
@@ -1916,7 +1916,7 @@
       </c>
       <c r="F2" s="9" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="G2" s="9" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="C3" s="10" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="D3" s="9" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="F3" s="9" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="G3" s="9" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr">
@@ -2083,7 +2083,7 @@
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="F6" s="9" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="H6" s="9" t="n"/>
@@ -2126,7 +2126,7 @@
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="F7" s="9" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="F8" s="9" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="G9" s="9" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="H9" s="9" t="n"/>
@@ -2232,6 +2232,18 @@
       <c r="L9" s="9" t="n"/>
       <c r="M9" s="9" t="n"/>
     </row>
+    <row r="10"/>
+    <row r="11"/>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
     <row r="22" ht="16" customHeight="1">
       <c r="H22" s="6" t="n"/>
     </row>
